--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-ballot</t>
+    <t>2.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -48,7 +48,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:44:45+00:00</t>
+    <t>2024-03-25T10:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-25T10:59:40+00:00</t>
+    <t>2024-03-25T11:06:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T08:02:06+00:00</t>
+    <t>2024-05-23T12:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:05:52+00:00</t>
+    <t>2024-05-23T12:32:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T12:32:02+00:00</t>
+    <t>2024-05-23T14:35:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-05-23T14:35:00+00:00</t>
+    <t>2024-06-11T15:33:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:12+00:00</t>
+    <t>2024-06-11T15:33:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-06-11T15:33:34+00:00</t>
+    <t>2024-07-02T12:51:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Interop'Santé (http://interopsante.org/)</t>
   </si>
   <si>
-    <t>InteropSanté (fhir@interopsante.org(WORK))</t>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-08T11:39:28+00:00</t>
+    <t>2024-07-17T12:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T12:13:27+00:00</t>
+    <t>2024-07-17T14:21:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.1</t>
+    <t>2.1.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T14:21:13+00:00</t>
+    <t>2024-07-17T15:15:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-17T15:15:49+00:00</t>
+    <t>2024-07-17T15:35:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T07:11:02+00:00</t>
+    <t>2024-07-25T15:28:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:28:42+00:00</t>
+    <t>2024-07-25T15:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:29:18+00:00</t>
+    <t>2024-07-25T15:44:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-25T15:44:10+00:00</t>
+    <t>2024-08-01T13:12:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0-ballot</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-03T15:38:30+00:00</t>
+    <t>2024-09-04T07:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T07:28:39+00:00</t>
+    <t>2024-09-04T07:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-06T12:53:53+00:00</t>
+    <t>2024-10-28T08:07:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:07:18+00:00</t>
+    <t>2024-10-28T08:08:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-28T08:08:30+00:00</t>
+    <t>2024-10-29T10:42:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:05:50+00:00</t>
+    <t>2025-01-28T09:07:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-28T09:07:36+00:00</t>
+    <t>2025-02-04T08:51:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T08:51:44+00:00</t>
+    <t>2025-02-04T09:30:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-04T09:30:35+00:00</t>
+    <t>2025-02-19T13:47:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:47:59+00:00</t>
+    <t>2025-02-19T13:52:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:52:01+00:00</t>
+    <t>2025-02-19T13:53:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:53:58+00:00</t>
+    <t>2025-02-19T13:58:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,9 @@
     <t>Description</t>
   </si>
   <si>
-    <t>This French extension allows to associate the type of service with the duration of this service | Cette extension française permet d'associer le type de service avec la durée de ce service.</t>
+    <t>Cette extension française permet d'associer le type de service avec la durée de ce service.
++This French extension allows to associate the type of service with the duration of this service</t>
   </si>
   <si>
     <t>Purpose</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T13:58:46+00:00</t>
+    <t>2025-02-19T14:07:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-19T14:07:54+00:00</t>
+    <t>2025-02-19T14:26:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-12T08:11:18+00:00</t>
+    <t>2025-05-20T13:27:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:27:17+00:00</t>
+    <t>2025-05-20T13:29:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:29:42+00:00</t>
+    <t>2025-05-20T13:48:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="567" uniqueCount="134">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T13:48:39+00:00</t>
+    <t>2025-06-04T13:32:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -383,6 +383,9 @@
   </si>
   <si>
     <t>example</t>
+  </si>
+  <si>
+    <t>This value set defines an example set of codes of service-types.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/service-type</t>
@@ -785,7 +788,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="51.35546875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="32.1953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -1700,9 +1703,11 @@
       <c r="X9" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="Y9" s="2"/>
+      <c r="Y9" t="s" s="2">
+        <v>120</v>
+      </c>
       <c r="Z9" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AA9" t="s" s="2">
         <v>79</v>
@@ -1720,7 +1725,7 @@
         <v>79</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>80</v>
@@ -1732,7 +1737,7 @@
         <v>79</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>113</v>
@@ -1740,13 +1745,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B10" t="s" s="2">
         <v>92</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>79</v>
@@ -1771,10 +1776,10 @@
         <v>93</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1845,7 +1850,7 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>103</v>
@@ -1948,7 +1953,7 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>105</v>
@@ -2051,7 +2056,7 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>107</v>
@@ -2094,7 +2099,7 @@
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>79</v>
@@ -2156,7 +2161,7 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B14" t="s" s="2">
         <v>115</v>
@@ -2182,7 +2187,7 @@
         <v>79</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L14" t="s" s="2">
         <v>117</v>
@@ -2239,7 +2244,7 @@
         <v>79</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>80</v>
@@ -2251,7 +2256,7 @@
         <v>79</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>113</v>
@@ -2364,10 +2369,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2390,7 +2395,7 @@
         <v>79</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L16" t="s" s="2">
         <v>117</v>
@@ -2447,7 +2452,7 @@
         <v>79</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>80</v>
@@ -2459,7 +2464,7 @@
         <v>79</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AK16" t="s" s="2">
         <v>113</v>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-04T13:32:30+00:00</t>
+    <t>2025-06-24T17:01:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-06-24T17:01:22+00:00</t>
+    <t>2025-07-04T12:19:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-04T12:19:33+00:00</t>
+    <t>2025-07-08T13:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-08T13:28:39+00:00</t>
+    <t>2025-07-16T09:34:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-16T09:34:35+00:00</t>
+    <t>2025-07-30T14:55:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-07-30T14:55:53+00:00</t>
+    <t>2025-10-08T07:32:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T07:32:57+00:00</t>
+    <t>2025-10-08T12:04:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-08T12:04:30+00:00</t>
+    <t>2025-10-08T16:01:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T10:25:45+00:00</t>
+    <t>2026-02-04T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T13:09:39+00:00</t>
+    <t>2026-02-09T06:47:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T06:47:58+00:00</t>
+    <t>2026-02-11T16:15:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-11T16:15:37+00:00</t>
+    <t>2026-02-17T10:02:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-17T10:02:14+00:00</t>
+    <t>2026-02-23T09:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T09:26:22+00:00</t>
+    <t>2026-02-23T10:39:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T10:39:10+00:00</t>
+    <t>2026-02-23T12:56:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T07:09:47+00:00</t>
+    <t>2026-03-25T10:22:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:11+00:00</t>
+    <t>2026-03-25T10:22:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:22:40+00:00</t>
+    <t>2026-03-25T10:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T10:25:13+00:00</t>
+    <t>2026-03-25T15:00:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-25T15:00:47+00:00</t>
+    <t>2026-03-31T09:16:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -78,7 +78,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-31T09:16:18+00:00</t>
+    <t>2026-05-07T06:38:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:50:40+00:00</t>
+    <t>2026-05-27T14:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T14:53:55+00:00</t>
+    <t>2026-05-28T14:22:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T14:22:24+00:00</t>
+    <t>2026-06-12T14:04:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:04:24+00:00</t>
+    <t>2026-06-12T14:05:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:05:00+00:00</t>
+    <t>2026-06-12T14:35:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T14:35:23+00:00</t>
+    <t>2026-06-26T12:32:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T12:32:04+00:00</t>
+    <t>2026-06-29T09:30:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T09:30:52+00:00</t>
+    <t>2026-07-22T12:21:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-22T12:21:07+00:00</t>
+    <t>2026-07-27T15:02:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T15:02:31+00:00</t>
+    <t>2026-08-03T12:52:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T12:52:25+00:00</t>
+    <t>2026-08-04T12:22:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:22:31+00:00</t>
+    <t>2026-08-04T12:29:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
+++ b/main/ig/StructureDefinition-fr-core-service-type-duration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-04T12:29:23+00:00</t>
+    <t>2026-08-10T16:34:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
